--- a/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.10ファイル管理.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.10ファイル管理.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7AFC1ED-ECAE-4014-B6D4-9169090FC84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A18EA5E-0E96-4EE7-8B2D-02E6531617FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1155" yWindow="-120" windowWidth="27765" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7.10.ファイル管理" sheetId="17" r:id="rId1"/>
@@ -475,10 +475,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>https://nablarch.github.io/docs/5u21/doc/application_framework/application_framework/libraries/file_path_management.html</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>削除は論理削除を行う仕様である。運用時には、別途、論理削除状態のレコードのデータクリーニングについて検討する必要がある。</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -506,6 +502,10 @@
     <rPh sb="38" eb="40">
       <t>サンショウ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/libraries/file_path_management.html</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -516,7 +516,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -591,6 +591,15 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color theme="10"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
       <color theme="10"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -966,8 +975,65 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="5">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="5" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1022,63 +1088,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1109,9 +1118,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1149,9 +1158,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1184,26 +1193,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1236,26 +1228,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1433,144 +1408,144 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI504"/>
-  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="3.6328125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="3.625" style="15"/>
+    <col min="1" max="16384" width="3.6328125" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="80"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="99"/>
       <c r="P1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q1" s="2"/>
-      <c r="R1" s="81" t="s">
+      <c r="R1" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="S1" s="82"/>
-      <c r="T1" s="82"/>
-      <c r="U1" s="82"/>
-      <c r="V1" s="82"/>
-      <c r="W1" s="82"/>
-      <c r="X1" s="83"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="64"/>
+      <c r="U1" s="64"/>
+      <c r="V1" s="64"/>
+      <c r="W1" s="64"/>
+      <c r="X1" s="65"/>
       <c r="Y1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="84"/>
-      <c r="AB1" s="85"/>
-      <c r="AC1" s="85"/>
-      <c r="AD1" s="85"/>
-      <c r="AE1" s="86"/>
-      <c r="AF1" s="87"/>
-      <c r="AG1" s="88"/>
-      <c r="AH1" s="88"/>
-      <c r="AI1" s="89"/>
-    </row>
-    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AA1" s="66"/>
+      <c r="AB1" s="67"/>
+      <c r="AC1" s="67"/>
+      <c r="AD1" s="67"/>
+      <c r="AE1" s="68"/>
+      <c r="AF1" s="69"/>
+      <c r="AG1" s="70"/>
+      <c r="AH1" s="70"/>
+      <c r="AI1" s="71"/>
+    </row>
+    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91"/>
-      <c r="I2" s="91"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="91"/>
-      <c r="L2" s="91"/>
-      <c r="M2" s="91"/>
-      <c r="N2" s="91"/>
-      <c r="O2" s="92"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
+      <c r="N2" s="73"/>
+      <c r="O2" s="74"/>
       <c r="P2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="Q2" s="8"/>
-      <c r="R2" s="93" t="s">
+      <c r="R2" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="S2" s="94"/>
-      <c r="T2" s="94"/>
-      <c r="U2" s="94"/>
-      <c r="V2" s="94"/>
-      <c r="W2" s="94"/>
-      <c r="X2" s="95"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
+      <c r="W2" s="76"/>
+      <c r="X2" s="77"/>
       <c r="Y2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="84"/>
-      <c r="AB2" s="85"/>
-      <c r="AC2" s="85"/>
-      <c r="AD2" s="85"/>
-      <c r="AE2" s="86"/>
-      <c r="AF2" s="87"/>
-      <c r="AG2" s="88"/>
-      <c r="AH2" s="88"/>
-      <c r="AI2" s="89"/>
-    </row>
-    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AA2" s="66"/>
+      <c r="AB2" s="67"/>
+      <c r="AC2" s="67"/>
+      <c r="AD2" s="67"/>
+      <c r="AE2" s="68"/>
+      <c r="AF2" s="69"/>
+      <c r="AG2" s="70"/>
+      <c r="AH2" s="70"/>
+      <c r="AI2" s="71"/>
+    </row>
+    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="10"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="99"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="99"/>
-      <c r="M3" s="99"/>
-      <c r="N3" s="99"/>
-      <c r="O3" s="99"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="81"/>
+      <c r="M3" s="81"/>
+      <c r="N3" s="81"/>
+      <c r="O3" s="81"/>
       <c r="P3" s="11"/>
       <c r="Q3" s="12"/>
-      <c r="R3" s="96"/>
-      <c r="S3" s="97"/>
-      <c r="T3" s="97"/>
-      <c r="U3" s="97"/>
-      <c r="V3" s="97"/>
-      <c r="W3" s="97"/>
-      <c r="X3" s="98"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="79"/>
+      <c r="U3" s="79"/>
+      <c r="V3" s="79"/>
+      <c r="W3" s="79"/>
+      <c r="X3" s="80"/>
       <c r="Y3" s="11" t="s">
         <v>7</v>
       </c>
       <c r="Z3" s="13"/>
-      <c r="AA3" s="84"/>
-      <c r="AB3" s="85"/>
-      <c r="AC3" s="85"/>
-      <c r="AD3" s="85"/>
-      <c r="AE3" s="86"/>
-      <c r="AF3" s="87"/>
-      <c r="AG3" s="88"/>
-      <c r="AH3" s="88"/>
-      <c r="AI3" s="89"/>
-    </row>
-    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AA3" s="66"/>
+      <c r="AB3" s="67"/>
+      <c r="AC3" s="67"/>
+      <c r="AD3" s="67"/>
+      <c r="AE3" s="68"/>
+      <c r="AF3" s="69"/>
+      <c r="AG3" s="70"/>
+      <c r="AH3" s="70"/>
+      <c r="AI3" s="71"/>
+    </row>
+    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="14" t="s">
         <v>13</v>
       </c>
@@ -1578,8 +1553,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="14" t="str">
         <f>$B$5&amp;"10."</f>
         <v>7.10.</v>
@@ -1588,7 +1563,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D8" s="20"/>
       <c r="E8" s="20"/>
       <c r="F8" s="20"/>
@@ -1621,7 +1596,7 @@
       <c r="AG8" s="20"/>
       <c r="AH8" s="20"/>
     </row>
-    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="21"/>
       <c r="B9" s="21"/>
       <c r="C9" s="21"/>
@@ -1663,7 +1638,7 @@
       <c r="AH9" s="21"/>
       <c r="AI9" s="21"/>
     </row>
-    <row r="10" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:35" ht="11" x14ac:dyDescent="0.2">
       <c r="A10" s="21"/>
       <c r="B10" s="21"/>
       <c r="C10" s="21"/>
@@ -1702,7 +1677,7 @@
       <c r="AH10" s="21"/>
       <c r="AI10" s="21"/>
     </row>
-    <row r="11" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:35" ht="11" x14ac:dyDescent="0.2">
       <c r="A11" s="21"/>
       <c r="B11" s="21"/>
       <c r="C11" s="21"/>
@@ -1739,7 +1714,7 @@
       <c r="AH11" s="21"/>
       <c r="AI11" s="21"/>
     </row>
-    <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="21"/>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
@@ -1778,7 +1753,7 @@
       <c r="AH12" s="21"/>
       <c r="AI12" s="21"/>
     </row>
-    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="21"/>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
@@ -1821,20 +1796,20 @@
       <c r="AH13" s="25"/>
       <c r="AI13" s="21"/>
     </row>
-    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="21"/>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
       <c r="D14" s="22"/>
-      <c r="E14" s="63" t="s">
+      <c r="E14" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="64"/>
-      <c r="K14" s="65"/>
+      <c r="F14" s="83"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="83"/>
+      <c r="I14" s="83"/>
+      <c r="J14" s="83"/>
+      <c r="K14" s="84"/>
       <c r="L14" s="41" t="s">
         <v>24</v>
       </c>
@@ -1864,18 +1839,18 @@
       <c r="AH14" s="43"/>
       <c r="AI14" s="21"/>
     </row>
-    <row r="15" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="21"/>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
       <c r="D15" s="22"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="67"/>
-      <c r="J15" s="67"/>
-      <c r="K15" s="68"/>
+      <c r="E15" s="85"/>
+      <c r="F15" s="86"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="86"/>
+      <c r="I15" s="86"/>
+      <c r="J15" s="86"/>
+      <c r="K15" s="87"/>
       <c r="L15" s="44"/>
       <c r="M15" s="45"/>
       <c r="N15" s="45"/>
@@ -1901,20 +1876,20 @@
       <c r="AH15" s="46"/>
       <c r="AI15" s="21"/>
     </row>
-    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="21"/>
       <c r="B16" s="21"/>
       <c r="C16" s="21"/>
       <c r="D16" s="22"/>
-      <c r="E16" s="63" t="s">
+      <c r="E16" s="82" t="s">
         <v>57</v>
       </c>
-      <c r="F16" s="64"/>
-      <c r="G16" s="64"/>
-      <c r="H16" s="64"/>
-      <c r="I16" s="64"/>
-      <c r="J16" s="64"/>
-      <c r="K16" s="65"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="83"/>
+      <c r="I16" s="83"/>
+      <c r="J16" s="83"/>
+      <c r="K16" s="84"/>
       <c r="L16" s="41" t="s">
         <v>59</v>
       </c>
@@ -1944,18 +1919,18 @@
       <c r="AH16" s="48"/>
       <c r="AI16" s="21"/>
     </row>
-    <row r="17" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="21"/>
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
       <c r="D17" s="22"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="67"/>
-      <c r="H17" s="67"/>
-      <c r="I17" s="67"/>
-      <c r="J17" s="67"/>
-      <c r="K17" s="68"/>
+      <c r="E17" s="85"/>
+      <c r="F17" s="86"/>
+      <c r="G17" s="86"/>
+      <c r="H17" s="86"/>
+      <c r="I17" s="86"/>
+      <c r="J17" s="86"/>
+      <c r="K17" s="87"/>
       <c r="L17" s="61" t="s">
         <v>60</v>
       </c>
@@ -1983,18 +1958,18 @@
       <c r="AH17" s="50"/>
       <c r="AI17" s="21"/>
     </row>
-    <row r="18" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="21"/>
       <c r="B18" s="21"/>
       <c r="C18" s="21"/>
       <c r="D18" s="22"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="70"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="70"/>
-      <c r="J18" s="70"/>
-      <c r="K18" s="71"/>
+      <c r="E18" s="88"/>
+      <c r="F18" s="89"/>
+      <c r="G18" s="89"/>
+      <c r="H18" s="89"/>
+      <c r="I18" s="89"/>
+      <c r="J18" s="89"/>
+      <c r="K18" s="90"/>
       <c r="L18" s="55"/>
       <c r="M18" s="56"/>
       <c r="N18" s="56"/>
@@ -2020,20 +1995,20 @@
       <c r="AH18" s="50"/>
       <c r="AI18" s="21"/>
     </row>
-    <row r="19" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="21"/>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
       <c r="D19" s="22"/>
-      <c r="E19" s="63" t="s">
+      <c r="E19" s="82" t="s">
         <v>56</v>
       </c>
-      <c r="F19" s="64"/>
-      <c r="G19" s="64"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="64"/>
-      <c r="K19" s="65"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="83"/>
+      <c r="I19" s="83"/>
+      <c r="J19" s="83"/>
+      <c r="K19" s="84"/>
       <c r="L19" s="55"/>
       <c r="M19" s="56"/>
       <c r="N19" s="56"/>
@@ -2059,18 +2034,18 @@
       <c r="AH19" s="50"/>
       <c r="AI19" s="21"/>
     </row>
-    <row r="20" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="21"/>
       <c r="B20" s="21"/>
       <c r="C20" s="21"/>
       <c r="D20" s="22"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="67"/>
-      <c r="G20" s="67"/>
-      <c r="H20" s="67"/>
-      <c r="I20" s="67"/>
-      <c r="J20" s="67"/>
-      <c r="K20" s="68"/>
+      <c r="E20" s="85"/>
+      <c r="F20" s="86"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="86"/>
+      <c r="I20" s="86"/>
+      <c r="J20" s="86"/>
+      <c r="K20" s="87"/>
       <c r="L20" s="55"/>
       <c r="M20" s="56"/>
       <c r="N20" s="56"/>
@@ -2096,18 +2071,18 @@
       <c r="AH20" s="50"/>
       <c r="AI20" s="21"/>
     </row>
-    <row r="21" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="21"/>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
       <c r="D21" s="22"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="70"/>
-      <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="70"/>
-      <c r="J21" s="70"/>
-      <c r="K21" s="71"/>
+      <c r="E21" s="88"/>
+      <c r="F21" s="89"/>
+      <c r="G21" s="89"/>
+      <c r="H21" s="89"/>
+      <c r="I21" s="89"/>
+      <c r="J21" s="89"/>
+      <c r="K21" s="90"/>
       <c r="L21" s="55"/>
       <c r="M21" s="56"/>
       <c r="N21" s="56"/>
@@ -2133,20 +2108,20 @@
       <c r="AH21" s="50"/>
       <c r="AI21" s="21"/>
     </row>
-    <row r="22" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="21"/>
       <c r="B22" s="21"/>
       <c r="C22" s="21"/>
       <c r="D22" s="22"/>
-      <c r="E22" s="72" t="s">
+      <c r="E22" s="91" t="s">
         <v>55</v>
       </c>
-      <c r="F22" s="73"/>
-      <c r="G22" s="73"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="73"/>
-      <c r="J22" s="73"/>
-      <c r="K22" s="74"/>
+      <c r="F22" s="92"/>
+      <c r="G22" s="92"/>
+      <c r="H22" s="92"/>
+      <c r="I22" s="92"/>
+      <c r="J22" s="92"/>
+      <c r="K22" s="93"/>
       <c r="L22" s="55"/>
       <c r="M22" s="56"/>
       <c r="N22" s="56"/>
@@ -2172,18 +2147,18 @@
       <c r="AH22" s="50"/>
       <c r="AI22" s="21"/>
     </row>
-    <row r="23" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="21"/>
       <c r="B23" s="21"/>
       <c r="C23" s="21"/>
       <c r="D23" s="22"/>
-      <c r="E23" s="75"/>
-      <c r="F23" s="76"/>
-      <c r="G23" s="76"/>
-      <c r="H23" s="76"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="76"/>
-      <c r="K23" s="77"/>
+      <c r="E23" s="94"/>
+      <c r="F23" s="95"/>
+      <c r="G23" s="95"/>
+      <c r="H23" s="95"/>
+      <c r="I23" s="95"/>
+      <c r="J23" s="95"/>
+      <c r="K23" s="96"/>
       <c r="L23" s="58"/>
       <c r="M23" s="59"/>
       <c r="N23" s="59"/>
@@ -2209,7 +2184,7 @@
       <c r="AH23" s="52"/>
       <c r="AI23" s="21"/>
     </row>
-    <row r="24" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="21"/>
       <c r="B24" s="21"/>
       <c r="C24" s="21"/>
@@ -2246,7 +2221,7 @@
       <c r="AH24" s="21"/>
       <c r="AI24" s="21"/>
     </row>
-    <row r="25" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="21"/>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
@@ -2283,7 +2258,7 @@
       <c r="AH25" s="21"/>
       <c r="AI25" s="21"/>
     </row>
-    <row r="26" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="21"/>
       <c r="B26" s="21"/>
       <c r="C26" s="21"/>
@@ -2325,7 +2300,7 @@
       <c r="AH26" s="21"/>
       <c r="AI26" s="21"/>
     </row>
-    <row r="27" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="21"/>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
@@ -2367,7 +2342,7 @@
       <c r="AH27" s="21"/>
       <c r="AI27" s="21"/>
     </row>
-    <row r="28" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="21"/>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
@@ -2408,7 +2383,7 @@
       <c r="AH28" s="21"/>
       <c r="AI28" s="21"/>
     </row>
-    <row r="29" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="21"/>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -2447,14 +2422,14 @@
       <c r="AH29" s="21"/>
       <c r="AI29" s="21"/>
     </row>
-    <row r="30" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="21"/>
       <c r="B30" s="21"/>
       <c r="C30" s="21"/>
       <c r="D30" s="28"/>
       <c r="E30" s="28"/>
       <c r="F30" s="29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G30" s="29"/>
       <c r="H30" s="29"/>
@@ -2486,7 +2461,7 @@
       <c r="AH30" s="21"/>
       <c r="AI30" s="21"/>
     </row>
-    <row r="31" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="21"/>
       <c r="B31" s="21"/>
       <c r="C31" s="21"/>
@@ -2525,7 +2500,7 @@
       <c r="AH31" s="21"/>
       <c r="AI31" s="21"/>
     </row>
-    <row r="32" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="21"/>
       <c r="B32" s="21"/>
       <c r="C32" s="21"/>
@@ -2564,7 +2539,7 @@
       <c r="AH32" s="21"/>
       <c r="AI32" s="21"/>
     </row>
-    <row r="33" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="21"/>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -2601,7 +2576,7 @@
       <c r="AH33" s="21"/>
       <c r="AI33" s="21"/>
     </row>
-    <row r="34" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="21"/>
       <c r="B34" s="21"/>
       <c r="C34" s="21"/>
@@ -2640,7 +2615,7 @@
       <c r="AH34" s="17"/>
       <c r="AI34" s="21"/>
     </row>
-    <row r="35" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="21"/>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
@@ -2679,7 +2654,7 @@
       <c r="AH35" s="17"/>
       <c r="AI35" s="21"/>
     </row>
-    <row r="36" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="21"/>
       <c r="B36" s="21"/>
       <c r="C36" s="21"/>
@@ -2724,7 +2699,7 @@
       <c r="AH36" s="32"/>
       <c r="AI36" s="21"/>
     </row>
-    <row r="37" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="21"/>
       <c r="B37" s="21"/>
       <c r="C37" s="21"/>
@@ -2769,7 +2744,7 @@
       <c r="AH37" s="35"/>
       <c r="AI37" s="21"/>
     </row>
-    <row r="38" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="21"/>
       <c r="B38" s="21"/>
       <c r="C38" s="21"/>
@@ -2806,7 +2781,7 @@
       <c r="AH38" s="38"/>
       <c r="AI38" s="21"/>
     </row>
-    <row r="39" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="21"/>
       <c r="B39" s="21"/>
       <c r="C39" s="21"/>
@@ -2851,7 +2826,7 @@
       <c r="AH39" s="35"/>
       <c r="AI39" s="21"/>
     </row>
-    <row r="40" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="21"/>
       <c r="B40" s="21"/>
       <c r="C40" s="21"/>
@@ -2888,7 +2863,7 @@
       <c r="AH40" s="38"/>
       <c r="AI40" s="21"/>
     </row>
-    <row r="41" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="21"/>
       <c r="B41" s="21"/>
       <c r="C41" s="21"/>
@@ -2933,7 +2908,7 @@
       <c r="AH41" s="35"/>
       <c r="AI41" s="21"/>
     </row>
-    <row r="42" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="21"/>
       <c r="B42" s="21"/>
       <c r="C42" s="21"/>
@@ -2972,7 +2947,7 @@
       <c r="AH42" s="35"/>
       <c r="AI42" s="21"/>
     </row>
-    <row r="43" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="21"/>
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
@@ -3011,7 +2986,7 @@
       <c r="AH43" s="35"/>
       <c r="AI43" s="21"/>
     </row>
-    <row r="44" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="21"/>
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
@@ -3048,14 +3023,14 @@
       <c r="AH44" s="38"/>
       <c r="AI44" s="21"/>
     </row>
-    <row r="45" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="21"/>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
       <c r="E45" s="17"/>
       <c r="F45" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G45" s="17"/>
       <c r="H45" s="17"/>
@@ -3087,7 +3062,7 @@
       <c r="AH45" s="17"/>
       <c r="AI45" s="21"/>
     </row>
-    <row r="46" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="21"/>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
@@ -3124,7 +3099,7 @@
       <c r="AH46" s="17"/>
       <c r="AI46" s="21"/>
     </row>
-    <row r="47" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="21"/>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
@@ -3165,7 +3140,7 @@
       <c r="AH47" s="21"/>
       <c r="AI47" s="21"/>
     </row>
-    <row r="48" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="21"/>
       <c r="B48" s="21"/>
       <c r="C48" s="21"/>
@@ -3204,7 +3179,7 @@
       <c r="AH48" s="21"/>
       <c r="AI48" s="21"/>
     </row>
-    <row r="49" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="21"/>
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
@@ -3243,7 +3218,7 @@
       <c r="AH49" s="21"/>
       <c r="AI49" s="21"/>
     </row>
-    <row r="50" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="21"/>
       <c r="B50" s="21"/>
       <c r="C50" s="21"/>
@@ -3282,7 +3257,7 @@
       <c r="AH50" s="21"/>
       <c r="AI50" s="21"/>
     </row>
-    <row r="51" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="21"/>
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
@@ -3319,7 +3294,7 @@
       <c r="AH51" s="21"/>
       <c r="AI51" s="21"/>
     </row>
-    <row r="52" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="21"/>
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
@@ -3361,7 +3336,7 @@
       <c r="AH52" s="21"/>
       <c r="AI52" s="21"/>
     </row>
-    <row r="53" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="21"/>
       <c r="B53" s="21"/>
       <c r="C53" s="21"/>
@@ -3402,7 +3377,7 @@
       <c r="AH53" s="17"/>
       <c r="AI53" s="21"/>
     </row>
-    <row r="54" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="21"/>
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
@@ -3441,7 +3416,7 @@
       <c r="AH54" s="17"/>
       <c r="AI54" s="21"/>
     </row>
-    <row r="55" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="21"/>
       <c r="B55" s="21"/>
       <c r="C55" s="21"/>
@@ -3480,7 +3455,7 @@
       <c r="AH55" s="17"/>
       <c r="AI55" s="21"/>
     </row>
-    <row r="56" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="21"/>
       <c r="B56" s="21"/>
       <c r="C56" s="21"/>
@@ -3519,7 +3494,7 @@
       <c r="AH56" s="17"/>
       <c r="AI56" s="21"/>
     </row>
-    <row r="57" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="21"/>
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
@@ -3556,14 +3531,14 @@
       <c r="AH57" s="17"/>
       <c r="AI57" s="21"/>
     </row>
-    <row r="58" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="21"/>
       <c r="B58" s="21"/>
       <c r="C58" s="21"/>
       <c r="D58" s="22"/>
       <c r="E58" s="40"/>
       <c r="F58" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G58" s="21"/>
       <c r="H58" s="21"/>
@@ -3595,14 +3570,14 @@
       <c r="AH58" s="17"/>
       <c r="AI58" s="21"/>
     </row>
-    <row r="59" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="21"/>
       <c r="B59" s="21"/>
       <c r="C59" s="21"/>
       <c r="D59" s="22"/>
       <c r="E59" s="40"/>
       <c r="F59" s="62" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G59" s="21"/>
       <c r="H59" s="21"/>
@@ -3634,7 +3609,7 @@
       <c r="AH59" s="17"/>
       <c r="AI59" s="21"/>
     </row>
-    <row r="60" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="21"/>
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
@@ -3671,7 +3646,7 @@
       <c r="AH60" s="17"/>
       <c r="AI60" s="21"/>
     </row>
-    <row r="61" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="21"/>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
@@ -3712,7 +3687,7 @@
       <c r="AH61" s="17"/>
       <c r="AI61" s="21"/>
     </row>
-    <row r="62" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="21"/>
       <c r="B62" s="21"/>
       <c r="C62" s="21"/>
@@ -3751,7 +3726,7 @@
       <c r="AH62" s="17"/>
       <c r="AI62" s="21"/>
     </row>
-    <row r="63" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D63" s="14"/>
       <c r="E63" s="14"/>
       <c r="F63" s="19"/>
@@ -3766,7 +3741,7 @@
       <c r="AG63" s="16"/>
       <c r="AH63" s="16"/>
     </row>
-    <row r="64" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E64" s="16"/>
       <c r="F64" s="18"/>
       <c r="T64" s="16"/>
@@ -3785,7 +3760,7 @@
       <c r="AG64" s="16"/>
       <c r="AH64" s="16"/>
     </row>
-    <row r="65" spans="4:34" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="4:34" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E65" s="14"/>
       <c r="U65" s="16"/>
       <c r="V65" s="16"/>
@@ -3802,453 +3777,458 @@
       <c r="AG65" s="16"/>
       <c r="AH65" s="16"/>
     </row>
-    <row r="66" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D66" s="14"/>
     </row>
-    <row r="67" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="68" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="69" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="70" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="71" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F71" s="14"/>
     </row>
-    <row r="72" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="73" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="74" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F74" s="14"/>
     </row>
-    <row r="75" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="76" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="78" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="79" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="80" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="81" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="82" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="83" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="84" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="85" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="86" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="87" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="88" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="89" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="90" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="91" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="92" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="93" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="94" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="95" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="96" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="97" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="98" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="99" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="100" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="101" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="102" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="103" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="104" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="105" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="106" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="107" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="108" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="109" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="110" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="111" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="112" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="113" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="114" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="115" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="116" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="117" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="118" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="119" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="120" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="121" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="122" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="123" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="124" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="125" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="126" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="75" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="E19:K21"/>
+    <mergeCell ref="E16:K18"/>
+    <mergeCell ref="E22:K23"/>
+    <mergeCell ref="E1:O1"/>
+    <mergeCell ref="E14:K15"/>
     <mergeCell ref="R1:X1"/>
     <mergeCell ref="AA1:AE1"/>
     <mergeCell ref="AF1:AI1"/>
@@ -4259,11 +4239,6 @@
     <mergeCell ref="E3:O3"/>
     <mergeCell ref="AA3:AE3"/>
     <mergeCell ref="AF3:AI3"/>
-    <mergeCell ref="E19:K21"/>
-    <mergeCell ref="E16:K18"/>
-    <mergeCell ref="E22:K23"/>
-    <mergeCell ref="E1:O1"/>
-    <mergeCell ref="E14:K15"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations disablePrompts="1" count="1">

--- a/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.10ファイル管理.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.10ファイル管理.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A18EA5E-0E96-4EE7-8B2D-02E6531617FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59B4499-2A9C-45BC-A21E-72C5B8E719DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -486,7 +486,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Nablarchの機能については、下記解説書の「7.5.ファイルパス管理」を参照。</t>
+    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/libraries/file_path_management.html</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Nablarchの機能については、下記解説書の「ファイルパス管理」を参照。</t>
     <rPh sb="9" eb="11">
       <t>キノウ</t>
     </rPh>
@@ -496,16 +500,12 @@
     <rPh sb="19" eb="22">
       <t>カイセツショ</t>
     </rPh>
+    <rPh sb="30" eb="32">
+      <t>カンリ</t>
+    </rPh>
     <rPh sb="34" eb="36">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
       <t>サンショウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/libraries/file_path_management.html</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -978,6 +978,60 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="5" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1034,60 +1088,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1420,43 +1420,43 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98"/>
-      <c r="O1" s="99"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="80"/>
       <c r="P1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q1" s="2"/>
-      <c r="R1" s="63" t="s">
+      <c r="R1" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="S1" s="64"/>
-      <c r="T1" s="64"/>
-      <c r="U1" s="64"/>
-      <c r="V1" s="64"/>
-      <c r="W1" s="64"/>
-      <c r="X1" s="65"/>
+      <c r="S1" s="82"/>
+      <c r="T1" s="82"/>
+      <c r="U1" s="82"/>
+      <c r="V1" s="82"/>
+      <c r="W1" s="82"/>
+      <c r="X1" s="83"/>
       <c r="Y1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="66"/>
-      <c r="AB1" s="67"/>
-      <c r="AC1" s="67"/>
-      <c r="AD1" s="67"/>
-      <c r="AE1" s="68"/>
-      <c r="AF1" s="69"/>
-      <c r="AG1" s="70"/>
-      <c r="AH1" s="70"/>
-      <c r="AI1" s="71"/>
+      <c r="AA1" s="84"/>
+      <c r="AB1" s="85"/>
+      <c r="AC1" s="85"/>
+      <c r="AD1" s="85"/>
+      <c r="AE1" s="86"/>
+      <c r="AF1" s="87"/>
+      <c r="AG1" s="88"/>
+      <c r="AH1" s="88"/>
+      <c r="AI1" s="89"/>
     </row>
     <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
@@ -1465,43 +1465,43 @@
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="74"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="91"/>
+      <c r="N2" s="91"/>
+      <c r="O2" s="92"/>
       <c r="P2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="Q2" s="8"/>
-      <c r="R2" s="75" t="s">
+      <c r="R2" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="76"/>
-      <c r="V2" s="76"/>
-      <c r="W2" s="76"/>
-      <c r="X2" s="77"/>
+      <c r="S2" s="94"/>
+      <c r="T2" s="94"/>
+      <c r="U2" s="94"/>
+      <c r="V2" s="94"/>
+      <c r="W2" s="94"/>
+      <c r="X2" s="95"/>
       <c r="Y2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="66"/>
-      <c r="AB2" s="67"/>
-      <c r="AC2" s="67"/>
-      <c r="AD2" s="67"/>
-      <c r="AE2" s="68"/>
-      <c r="AF2" s="69"/>
-      <c r="AG2" s="70"/>
-      <c r="AH2" s="70"/>
-      <c r="AI2" s="71"/>
+      <c r="AA2" s="84"/>
+      <c r="AB2" s="85"/>
+      <c r="AC2" s="85"/>
+      <c r="AD2" s="85"/>
+      <c r="AE2" s="86"/>
+      <c r="AF2" s="87"/>
+      <c r="AG2" s="88"/>
+      <c r="AH2" s="88"/>
+      <c r="AI2" s="89"/>
     </row>
     <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -1510,39 +1510,39 @@
       <c r="B3" s="9"/>
       <c r="C3" s="10"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81"/>
-      <c r="L3" s="81"/>
-      <c r="M3" s="81"/>
-      <c r="N3" s="81"/>
-      <c r="O3" s="81"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="99"/>
+      <c r="K3" s="99"/>
+      <c r="L3" s="99"/>
+      <c r="M3" s="99"/>
+      <c r="N3" s="99"/>
+      <c r="O3" s="99"/>
       <c r="P3" s="11"/>
       <c r="Q3" s="12"/>
-      <c r="R3" s="78"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="79"/>
-      <c r="U3" s="79"/>
-      <c r="V3" s="79"/>
-      <c r="W3" s="79"/>
-      <c r="X3" s="80"/>
+      <c r="R3" s="96"/>
+      <c r="S3" s="97"/>
+      <c r="T3" s="97"/>
+      <c r="U3" s="97"/>
+      <c r="V3" s="97"/>
+      <c r="W3" s="97"/>
+      <c r="X3" s="98"/>
       <c r="Y3" s="11" t="s">
         <v>7</v>
       </c>
       <c r="Z3" s="13"/>
-      <c r="AA3" s="66"/>
-      <c r="AB3" s="67"/>
-      <c r="AC3" s="67"/>
-      <c r="AD3" s="67"/>
-      <c r="AE3" s="68"/>
-      <c r="AF3" s="69"/>
-      <c r="AG3" s="70"/>
-      <c r="AH3" s="70"/>
-      <c r="AI3" s="71"/>
+      <c r="AA3" s="84"/>
+      <c r="AB3" s="85"/>
+      <c r="AC3" s="85"/>
+      <c r="AD3" s="85"/>
+      <c r="AE3" s="86"/>
+      <c r="AF3" s="87"/>
+      <c r="AG3" s="88"/>
+      <c r="AH3" s="88"/>
+      <c r="AI3" s="89"/>
     </row>
     <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1801,15 +1801,15 @@
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
       <c r="D14" s="22"/>
-      <c r="E14" s="82" t="s">
+      <c r="E14" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="F14" s="83"/>
-      <c r="G14" s="83"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="83"/>
-      <c r="J14" s="83"/>
-      <c r="K14" s="84"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="65"/>
       <c r="L14" s="41" t="s">
         <v>24</v>
       </c>
@@ -1844,13 +1844,13 @@
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
       <c r="D15" s="22"/>
-      <c r="E15" s="85"/>
-      <c r="F15" s="86"/>
-      <c r="G15" s="86"/>
-      <c r="H15" s="86"/>
-      <c r="I15" s="86"/>
-      <c r="J15" s="86"/>
-      <c r="K15" s="87"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="67"/>
+      <c r="J15" s="67"/>
+      <c r="K15" s="68"/>
       <c r="L15" s="44"/>
       <c r="M15" s="45"/>
       <c r="N15" s="45"/>
@@ -1881,15 +1881,15 @@
       <c r="B16" s="21"/>
       <c r="C16" s="21"/>
       <c r="D16" s="22"/>
-      <c r="E16" s="82" t="s">
+      <c r="E16" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="F16" s="83"/>
-      <c r="G16" s="83"/>
-      <c r="H16" s="83"/>
-      <c r="I16" s="83"/>
-      <c r="J16" s="83"/>
-      <c r="K16" s="84"/>
+      <c r="F16" s="64"/>
+      <c r="G16" s="64"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="64"/>
+      <c r="K16" s="65"/>
       <c r="L16" s="41" t="s">
         <v>59</v>
       </c>
@@ -1924,13 +1924,13 @@
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
       <c r="D17" s="22"/>
-      <c r="E17" s="85"/>
-      <c r="F17" s="86"/>
-      <c r="G17" s="86"/>
-      <c r="H17" s="86"/>
-      <c r="I17" s="86"/>
-      <c r="J17" s="86"/>
-      <c r="K17" s="87"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="67"/>
+      <c r="H17" s="67"/>
+      <c r="I17" s="67"/>
+      <c r="J17" s="67"/>
+      <c r="K17" s="68"/>
       <c r="L17" s="61" t="s">
         <v>60</v>
       </c>
@@ -1963,13 +1963,13 @@
       <c r="B18" s="21"/>
       <c r="C18" s="21"/>
       <c r="D18" s="22"/>
-      <c r="E18" s="88"/>
-      <c r="F18" s="89"/>
-      <c r="G18" s="89"/>
-      <c r="H18" s="89"/>
-      <c r="I18" s="89"/>
-      <c r="J18" s="89"/>
-      <c r="K18" s="90"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="70"/>
+      <c r="K18" s="71"/>
       <c r="L18" s="55"/>
       <c r="M18" s="56"/>
       <c r="N18" s="56"/>
@@ -2000,15 +2000,15 @@
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
       <c r="D19" s="22"/>
-      <c r="E19" s="82" t="s">
+      <c r="E19" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="F19" s="83"/>
-      <c r="G19" s="83"/>
-      <c r="H19" s="83"/>
-      <c r="I19" s="83"/>
-      <c r="J19" s="83"/>
-      <c r="K19" s="84"/>
+      <c r="F19" s="64"/>
+      <c r="G19" s="64"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="64"/>
+      <c r="J19" s="64"/>
+      <c r="K19" s="65"/>
       <c r="L19" s="55"/>
       <c r="M19" s="56"/>
       <c r="N19" s="56"/>
@@ -2039,13 +2039,13 @@
       <c r="B20" s="21"/>
       <c r="C20" s="21"/>
       <c r="D20" s="22"/>
-      <c r="E20" s="85"/>
-      <c r="F20" s="86"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="86"/>
-      <c r="I20" s="86"/>
-      <c r="J20" s="86"/>
-      <c r="K20" s="87"/>
+      <c r="E20" s="66"/>
+      <c r="F20" s="67"/>
+      <c r="G20" s="67"/>
+      <c r="H20" s="67"/>
+      <c r="I20" s="67"/>
+      <c r="J20" s="67"/>
+      <c r="K20" s="68"/>
       <c r="L20" s="55"/>
       <c r="M20" s="56"/>
       <c r="N20" s="56"/>
@@ -2076,13 +2076,13 @@
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
       <c r="D21" s="22"/>
-      <c r="E21" s="88"/>
-      <c r="F21" s="89"/>
-      <c r="G21" s="89"/>
-      <c r="H21" s="89"/>
-      <c r="I21" s="89"/>
-      <c r="J21" s="89"/>
-      <c r="K21" s="90"/>
+      <c r="E21" s="69"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="70"/>
+      <c r="J21" s="70"/>
+      <c r="K21" s="71"/>
       <c r="L21" s="55"/>
       <c r="M21" s="56"/>
       <c r="N21" s="56"/>
@@ -2113,15 +2113,15 @@
       <c r="B22" s="21"/>
       <c r="C22" s="21"/>
       <c r="D22" s="22"/>
-      <c r="E22" s="91" t="s">
+      <c r="E22" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="F22" s="92"/>
-      <c r="G22" s="92"/>
-      <c r="H22" s="92"/>
-      <c r="I22" s="92"/>
-      <c r="J22" s="92"/>
-      <c r="K22" s="93"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="73"/>
+      <c r="K22" s="74"/>
       <c r="L22" s="55"/>
       <c r="M22" s="56"/>
       <c r="N22" s="56"/>
@@ -2152,13 +2152,13 @@
       <c r="B23" s="21"/>
       <c r="C23" s="21"/>
       <c r="D23" s="22"/>
-      <c r="E23" s="94"/>
-      <c r="F23" s="95"/>
-      <c r="G23" s="95"/>
-      <c r="H23" s="95"/>
-      <c r="I23" s="95"/>
-      <c r="J23" s="95"/>
-      <c r="K23" s="96"/>
+      <c r="E23" s="75"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="76"/>
+      <c r="J23" s="76"/>
+      <c r="K23" s="77"/>
       <c r="L23" s="58"/>
       <c r="M23" s="59"/>
       <c r="N23" s="59"/>
@@ -3538,7 +3538,7 @@
       <c r="D58" s="22"/>
       <c r="E58" s="40"/>
       <c r="F58" s="21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G58" s="21"/>
       <c r="H58" s="21"/>
@@ -3577,7 +3577,7 @@
       <c r="D59" s="22"/>
       <c r="E59" s="40"/>
       <c r="F59" s="62" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G59" s="21"/>
       <c r="H59" s="21"/>
@@ -4224,11 +4224,6 @@
     <row r="504" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="E19:K21"/>
-    <mergeCell ref="E16:K18"/>
-    <mergeCell ref="E22:K23"/>
-    <mergeCell ref="E1:O1"/>
-    <mergeCell ref="E14:K15"/>
     <mergeCell ref="R1:X1"/>
     <mergeCell ref="AA1:AE1"/>
     <mergeCell ref="AF1:AI1"/>
@@ -4239,6 +4234,11 @@
     <mergeCell ref="E3:O3"/>
     <mergeCell ref="AA3:AE3"/>
     <mergeCell ref="AF3:AI3"/>
+    <mergeCell ref="E19:K21"/>
+    <mergeCell ref="E16:K18"/>
+    <mergeCell ref="E22:K23"/>
+    <mergeCell ref="E1:O1"/>
+    <mergeCell ref="E14:K15"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations disablePrompts="1" count="1">

--- a/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.10ファイル管理.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.10ファイル管理.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7AFC1ED-ECAE-4014-B6D4-9169090FC84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59B4499-2A9C-45BC-A21E-72C5B8E719DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1155" yWindow="-120" windowWidth="27765" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7.10.ファイル管理" sheetId="17" r:id="rId1"/>
@@ -475,10 +475,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>https://nablarch.github.io/docs/5u21/doc/application_framework/application_framework/libraries/file_path_management.html</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>削除は論理削除を行う仕様である。運用時には、別途、論理削除状態のレコードのデータクリーニングについて検討する必要がある。</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -490,7 +486,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Nablarchの機能については、下記解説書の「7.5.ファイルパス管理」を参照。</t>
+    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/libraries/file_path_management.html</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Nablarchの機能については、下記解説書の「ファイルパス管理」を参照。</t>
     <rPh sb="9" eb="11">
       <t>キノウ</t>
     </rPh>
@@ -500,10 +500,10 @@
     <rPh sb="19" eb="22">
       <t>カイセツショ</t>
     </rPh>
+    <rPh sb="30" eb="32">
+      <t>カンリ</t>
+    </rPh>
     <rPh sb="34" eb="36">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
       <t>サンショウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
@@ -516,7 +516,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -591,6 +591,15 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color theme="10"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
       <color theme="10"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -966,7 +975,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="5">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="5" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1109,9 +1118,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1149,9 +1158,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1184,26 +1193,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1236,26 +1228,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1433,12 +1408,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI504"/>
-  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="3.6328125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="3.625" style="15"/>
+    <col min="1" max="16384" width="3.6328125" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1483,7 +1458,7 @@
       <c r="AH1" s="88"/>
       <c r="AI1" s="89"/>
     </row>
-    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -1528,7 +1503,7 @@
       <c r="AH2" s="88"/>
       <c r="AI2" s="89"/>
     </row>
-    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1569,8 +1544,8 @@
       <c r="AH3" s="88"/>
       <c r="AI3" s="89"/>
     </row>
-    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="14" t="s">
         <v>13</v>
       </c>
@@ -1578,8 +1553,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="14" t="str">
         <f>$B$5&amp;"10."</f>
         <v>7.10.</v>
@@ -1588,7 +1563,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D8" s="20"/>
       <c r="E8" s="20"/>
       <c r="F8" s="20"/>
@@ -1621,7 +1596,7 @@
       <c r="AG8" s="20"/>
       <c r="AH8" s="20"/>
     </row>
-    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="21"/>
       <c r="B9" s="21"/>
       <c r="C9" s="21"/>
@@ -1663,7 +1638,7 @@
       <c r="AH9" s="21"/>
       <c r="AI9" s="21"/>
     </row>
-    <row r="10" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:35" ht="11" x14ac:dyDescent="0.2">
       <c r="A10" s="21"/>
       <c r="B10" s="21"/>
       <c r="C10" s="21"/>
@@ -1702,7 +1677,7 @@
       <c r="AH10" s="21"/>
       <c r="AI10" s="21"/>
     </row>
-    <row r="11" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:35" ht="11" x14ac:dyDescent="0.2">
       <c r="A11" s="21"/>
       <c r="B11" s="21"/>
       <c r="C11" s="21"/>
@@ -1739,7 +1714,7 @@
       <c r="AH11" s="21"/>
       <c r="AI11" s="21"/>
     </row>
-    <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="21"/>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
@@ -1778,7 +1753,7 @@
       <c r="AH12" s="21"/>
       <c r="AI12" s="21"/>
     </row>
-    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="21"/>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
@@ -1821,7 +1796,7 @@
       <c r="AH13" s="25"/>
       <c r="AI13" s="21"/>
     </row>
-    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="21"/>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
@@ -1864,7 +1839,7 @@
       <c r="AH14" s="43"/>
       <c r="AI14" s="21"/>
     </row>
-    <row r="15" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="21"/>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
@@ -1901,7 +1876,7 @@
       <c r="AH15" s="46"/>
       <c r="AI15" s="21"/>
     </row>
-    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="21"/>
       <c r="B16" s="21"/>
       <c r="C16" s="21"/>
@@ -1944,7 +1919,7 @@
       <c r="AH16" s="48"/>
       <c r="AI16" s="21"/>
     </row>
-    <row r="17" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="21"/>
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
@@ -1983,7 +1958,7 @@
       <c r="AH17" s="50"/>
       <c r="AI17" s="21"/>
     </row>
-    <row r="18" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="21"/>
       <c r="B18" s="21"/>
       <c r="C18" s="21"/>
@@ -2020,7 +1995,7 @@
       <c r="AH18" s="50"/>
       <c r="AI18" s="21"/>
     </row>
-    <row r="19" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="21"/>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
@@ -2059,7 +2034,7 @@
       <c r="AH19" s="50"/>
       <c r="AI19" s="21"/>
     </row>
-    <row r="20" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="21"/>
       <c r="B20" s="21"/>
       <c r="C20" s="21"/>
@@ -2096,7 +2071,7 @@
       <c r="AH20" s="50"/>
       <c r="AI20" s="21"/>
     </row>
-    <row r="21" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="21"/>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
@@ -2133,7 +2108,7 @@
       <c r="AH21" s="50"/>
       <c r="AI21" s="21"/>
     </row>
-    <row r="22" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="21"/>
       <c r="B22" s="21"/>
       <c r="C22" s="21"/>
@@ -2172,7 +2147,7 @@
       <c r="AH22" s="50"/>
       <c r="AI22" s="21"/>
     </row>
-    <row r="23" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="21"/>
       <c r="B23" s="21"/>
       <c r="C23" s="21"/>
@@ -2209,7 +2184,7 @@
       <c r="AH23" s="52"/>
       <c r="AI23" s="21"/>
     </row>
-    <row r="24" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="21"/>
       <c r="B24" s="21"/>
       <c r="C24" s="21"/>
@@ -2246,7 +2221,7 @@
       <c r="AH24" s="21"/>
       <c r="AI24" s="21"/>
     </row>
-    <row r="25" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="21"/>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
@@ -2283,7 +2258,7 @@
       <c r="AH25" s="21"/>
       <c r="AI25" s="21"/>
     </row>
-    <row r="26" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="21"/>
       <c r="B26" s="21"/>
       <c r="C26" s="21"/>
@@ -2325,7 +2300,7 @@
       <c r="AH26" s="21"/>
       <c r="AI26" s="21"/>
     </row>
-    <row r="27" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="21"/>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
@@ -2367,7 +2342,7 @@
       <c r="AH27" s="21"/>
       <c r="AI27" s="21"/>
     </row>
-    <row r="28" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="21"/>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
@@ -2408,7 +2383,7 @@
       <c r="AH28" s="21"/>
       <c r="AI28" s="21"/>
     </row>
-    <row r="29" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="21"/>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -2447,14 +2422,14 @@
       <c r="AH29" s="21"/>
       <c r="AI29" s="21"/>
     </row>
-    <row r="30" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="21"/>
       <c r="B30" s="21"/>
       <c r="C30" s="21"/>
       <c r="D30" s="28"/>
       <c r="E30" s="28"/>
       <c r="F30" s="29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G30" s="29"/>
       <c r="H30" s="29"/>
@@ -2486,7 +2461,7 @@
       <c r="AH30" s="21"/>
       <c r="AI30" s="21"/>
     </row>
-    <row r="31" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="21"/>
       <c r="B31" s="21"/>
       <c r="C31" s="21"/>
@@ -2525,7 +2500,7 @@
       <c r="AH31" s="21"/>
       <c r="AI31" s="21"/>
     </row>
-    <row r="32" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="21"/>
       <c r="B32" s="21"/>
       <c r="C32" s="21"/>
@@ -2564,7 +2539,7 @@
       <c r="AH32" s="21"/>
       <c r="AI32" s="21"/>
     </row>
-    <row r="33" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="21"/>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -2601,7 +2576,7 @@
       <c r="AH33" s="21"/>
       <c r="AI33" s="21"/>
     </row>
-    <row r="34" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="21"/>
       <c r="B34" s="21"/>
       <c r="C34" s="21"/>
@@ -2640,7 +2615,7 @@
       <c r="AH34" s="17"/>
       <c r="AI34" s="21"/>
     </row>
-    <row r="35" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="21"/>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
@@ -2679,7 +2654,7 @@
       <c r="AH35" s="17"/>
       <c r="AI35" s="21"/>
     </row>
-    <row r="36" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="21"/>
       <c r="B36" s="21"/>
       <c r="C36" s="21"/>
@@ -2724,7 +2699,7 @@
       <c r="AH36" s="32"/>
       <c r="AI36" s="21"/>
     </row>
-    <row r="37" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="21"/>
       <c r="B37" s="21"/>
       <c r="C37" s="21"/>
@@ -2769,7 +2744,7 @@
       <c r="AH37" s="35"/>
       <c r="AI37" s="21"/>
     </row>
-    <row r="38" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="21"/>
       <c r="B38" s="21"/>
       <c r="C38" s="21"/>
@@ -2806,7 +2781,7 @@
       <c r="AH38" s="38"/>
       <c r="AI38" s="21"/>
     </row>
-    <row r="39" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="21"/>
       <c r="B39" s="21"/>
       <c r="C39" s="21"/>
@@ -2851,7 +2826,7 @@
       <c r="AH39" s="35"/>
       <c r="AI39" s="21"/>
     </row>
-    <row r="40" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="21"/>
       <c r="B40" s="21"/>
       <c r="C40" s="21"/>
@@ -2888,7 +2863,7 @@
       <c r="AH40" s="38"/>
       <c r="AI40" s="21"/>
     </row>
-    <row r="41" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="21"/>
       <c r="B41" s="21"/>
       <c r="C41" s="21"/>
@@ -2933,7 +2908,7 @@
       <c r="AH41" s="35"/>
       <c r="AI41" s="21"/>
     </row>
-    <row r="42" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="21"/>
       <c r="B42" s="21"/>
       <c r="C42" s="21"/>
@@ -2972,7 +2947,7 @@
       <c r="AH42" s="35"/>
       <c r="AI42" s="21"/>
     </row>
-    <row r="43" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="21"/>
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
@@ -3011,7 +2986,7 @@
       <c r="AH43" s="35"/>
       <c r="AI43" s="21"/>
     </row>
-    <row r="44" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="21"/>
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
@@ -3048,14 +3023,14 @@
       <c r="AH44" s="38"/>
       <c r="AI44" s="21"/>
     </row>
-    <row r="45" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="21"/>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
       <c r="E45" s="17"/>
       <c r="F45" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G45" s="17"/>
       <c r="H45" s="17"/>
@@ -3087,7 +3062,7 @@
       <c r="AH45" s="17"/>
       <c r="AI45" s="21"/>
     </row>
-    <row r="46" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="21"/>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
@@ -3124,7 +3099,7 @@
       <c r="AH46" s="17"/>
       <c r="AI46" s="21"/>
     </row>
-    <row r="47" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="21"/>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
@@ -3165,7 +3140,7 @@
       <c r="AH47" s="21"/>
       <c r="AI47" s="21"/>
     </row>
-    <row r="48" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="21"/>
       <c r="B48" s="21"/>
       <c r="C48" s="21"/>
@@ -3204,7 +3179,7 @@
       <c r="AH48" s="21"/>
       <c r="AI48" s="21"/>
     </row>
-    <row r="49" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="21"/>
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
@@ -3243,7 +3218,7 @@
       <c r="AH49" s="21"/>
       <c r="AI49" s="21"/>
     </row>
-    <row r="50" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="21"/>
       <c r="B50" s="21"/>
       <c r="C50" s="21"/>
@@ -3282,7 +3257,7 @@
       <c r="AH50" s="21"/>
       <c r="AI50" s="21"/>
     </row>
-    <row r="51" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="21"/>
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
@@ -3319,7 +3294,7 @@
       <c r="AH51" s="21"/>
       <c r="AI51" s="21"/>
     </row>
-    <row r="52" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="21"/>
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
@@ -3361,7 +3336,7 @@
       <c r="AH52" s="21"/>
       <c r="AI52" s="21"/>
     </row>
-    <row r="53" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="21"/>
       <c r="B53" s="21"/>
       <c r="C53" s="21"/>
@@ -3402,7 +3377,7 @@
       <c r="AH53" s="17"/>
       <c r="AI53" s="21"/>
     </row>
-    <row r="54" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="21"/>
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
@@ -3441,7 +3416,7 @@
       <c r="AH54" s="17"/>
       <c r="AI54" s="21"/>
     </row>
-    <row r="55" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="21"/>
       <c r="B55" s="21"/>
       <c r="C55" s="21"/>
@@ -3480,7 +3455,7 @@
       <c r="AH55" s="17"/>
       <c r="AI55" s="21"/>
     </row>
-    <row r="56" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="21"/>
       <c r="B56" s="21"/>
       <c r="C56" s="21"/>
@@ -3519,7 +3494,7 @@
       <c r="AH56" s="17"/>
       <c r="AI56" s="21"/>
     </row>
-    <row r="57" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="21"/>
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
@@ -3556,7 +3531,7 @@
       <c r="AH57" s="17"/>
       <c r="AI57" s="21"/>
     </row>
-    <row r="58" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="21"/>
       <c r="B58" s="21"/>
       <c r="C58" s="21"/>
@@ -3595,14 +3570,14 @@
       <c r="AH58" s="17"/>
       <c r="AI58" s="21"/>
     </row>
-    <row r="59" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="21"/>
       <c r="B59" s="21"/>
       <c r="C59" s="21"/>
       <c r="D59" s="22"/>
       <c r="E59" s="40"/>
       <c r="F59" s="62" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G59" s="21"/>
       <c r="H59" s="21"/>
@@ -3634,7 +3609,7 @@
       <c r="AH59" s="17"/>
       <c r="AI59" s="21"/>
     </row>
-    <row r="60" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="21"/>
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
@@ -3671,7 +3646,7 @@
       <c r="AH60" s="17"/>
       <c r="AI60" s="21"/>
     </row>
-    <row r="61" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="21"/>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
@@ -3712,7 +3687,7 @@
       <c r="AH61" s="17"/>
       <c r="AI61" s="21"/>
     </row>
-    <row r="62" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="21"/>
       <c r="B62" s="21"/>
       <c r="C62" s="21"/>
@@ -3751,7 +3726,7 @@
       <c r="AH62" s="17"/>
       <c r="AI62" s="21"/>
     </row>
-    <row r="63" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D63" s="14"/>
       <c r="E63" s="14"/>
       <c r="F63" s="19"/>
@@ -3766,7 +3741,7 @@
       <c r="AG63" s="16"/>
       <c r="AH63" s="16"/>
     </row>
-    <row r="64" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E64" s="16"/>
       <c r="F64" s="18"/>
       <c r="T64" s="16"/>
@@ -3785,7 +3760,7 @@
       <c r="AG64" s="16"/>
       <c r="AH64" s="16"/>
     </row>
-    <row r="65" spans="4:34" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="4:34" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E65" s="14"/>
       <c r="U65" s="16"/>
       <c r="V65" s="16"/>
@@ -3802,451 +3777,451 @@
       <c r="AG65" s="16"/>
       <c r="AH65" s="16"/>
     </row>
-    <row r="66" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D66" s="14"/>
     </row>
-    <row r="67" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="68" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="69" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="70" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="71" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F71" s="14"/>
     </row>
-    <row r="72" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="73" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="74" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F74" s="14"/>
     </row>
-    <row r="75" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="76" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="78" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="79" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="80" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="81" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="82" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="83" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="84" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="85" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="86" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="87" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="88" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="89" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="90" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="91" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="92" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="93" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="94" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="95" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="96" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="97" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="98" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="99" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="100" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="101" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="102" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="103" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="104" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="105" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="106" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="107" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="108" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="109" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="110" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="111" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="112" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="113" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="114" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="115" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="116" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="117" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="118" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="119" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="120" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="121" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="122" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="123" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="124" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="125" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="126" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="75" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="R1:X1"/>

--- a/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.10ファイル管理.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_7処理方式共通_7.10ファイル管理.xlsx
@@ -1,22 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59B4499-2A9C-45BC-A21E-72C5B8E719DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26130"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E50EB93-B918-4D68-A0F1-967723BFA2A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1245" yWindow="-120" windowWidth="27675" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7.10.ファイル管理" sheetId="17" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'7.10.ファイル管理'!$A$1:$AI$65</definedName>
-    <definedName name="Z_344DE406_F393_4E5A_9A14_596BA958D606_.wvu.PrintArea" localSheetId="0" hidden="1">'7.10.ファイル管理'!$A$1:$AI$73</definedName>
-    <definedName name="Z_AC3D26AC_6835_49DE_BCEC_94F40C257790_.wvu.PrintArea" localSheetId="0" hidden="1">'7.10.ファイル管理'!$A$1:$AI$73</definedName>
-    <definedName name="Z_B9596DFB_62BC_4685_B6E9_D37718868A8E_.wvu.PrintArea" localSheetId="0" hidden="1">'7.10.ファイル管理'!$A$1:$AI$73</definedName>
-    <definedName name="Z_E93A55B4_B092_4477_988B_A2DD8C792DE3_.wvu.PrintArea" localSheetId="0" hidden="1">'7.10.ファイル管理'!$A$1:$AI$73</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -978,6 +971,63 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="5" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1031,63 +1081,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1118,9 +1111,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1158,9 +1151,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1193,9 +1186,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1228,9 +1238,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1404,148 +1431,148 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI504"/>
-  <sheetFormatPr defaultColWidth="3.6328125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="16384" width="3.6328125" style="15"/>
+    <col min="1" max="16384" width="3.625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="80"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="99"/>
       <c r="P1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q1" s="2"/>
-      <c r="R1" s="81" t="s">
+      <c r="R1" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="S1" s="82"/>
-      <c r="T1" s="82"/>
-      <c r="U1" s="82"/>
-      <c r="V1" s="82"/>
-      <c r="W1" s="82"/>
-      <c r="X1" s="83"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="64"/>
+      <c r="U1" s="64"/>
+      <c r="V1" s="64"/>
+      <c r="W1" s="64"/>
+      <c r="X1" s="65"/>
       <c r="Y1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="84"/>
-      <c r="AB1" s="85"/>
-      <c r="AC1" s="85"/>
-      <c r="AD1" s="85"/>
-      <c r="AE1" s="86"/>
-      <c r="AF1" s="87"/>
-      <c r="AG1" s="88"/>
-      <c r="AH1" s="88"/>
-      <c r="AI1" s="89"/>
-    </row>
-    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA1" s="66"/>
+      <c r="AB1" s="67"/>
+      <c r="AC1" s="67"/>
+      <c r="AD1" s="67"/>
+      <c r="AE1" s="68"/>
+      <c r="AF1" s="69"/>
+      <c r="AG1" s="70"/>
+      <c r="AH1" s="70"/>
+      <c r="AI1" s="71"/>
+    </row>
+    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91"/>
-      <c r="I2" s="91"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="91"/>
-      <c r="L2" s="91"/>
-      <c r="M2" s="91"/>
-      <c r="N2" s="91"/>
-      <c r="O2" s="92"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
+      <c r="N2" s="73"/>
+      <c r="O2" s="74"/>
       <c r="P2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="Q2" s="8"/>
-      <c r="R2" s="93" t="s">
+      <c r="R2" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="S2" s="94"/>
-      <c r="T2" s="94"/>
-      <c r="U2" s="94"/>
-      <c r="V2" s="94"/>
-      <c r="W2" s="94"/>
-      <c r="X2" s="95"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
+      <c r="W2" s="76"/>
+      <c r="X2" s="77"/>
       <c r="Y2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="84"/>
-      <c r="AB2" s="85"/>
-      <c r="AC2" s="85"/>
-      <c r="AD2" s="85"/>
-      <c r="AE2" s="86"/>
-      <c r="AF2" s="87"/>
-      <c r="AG2" s="88"/>
-      <c r="AH2" s="88"/>
-      <c r="AI2" s="89"/>
-    </row>
-    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA2" s="66"/>
+      <c r="AB2" s="67"/>
+      <c r="AC2" s="67"/>
+      <c r="AD2" s="67"/>
+      <c r="AE2" s="68"/>
+      <c r="AF2" s="69"/>
+      <c r="AG2" s="70"/>
+      <c r="AH2" s="70"/>
+      <c r="AI2" s="71"/>
+    </row>
+    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="10"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="99"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="99"/>
-      <c r="M3" s="99"/>
-      <c r="N3" s="99"/>
-      <c r="O3" s="99"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="81"/>
+      <c r="M3" s="81"/>
+      <c r="N3" s="81"/>
+      <c r="O3" s="81"/>
       <c r="P3" s="11"/>
       <c r="Q3" s="12"/>
-      <c r="R3" s="96"/>
-      <c r="S3" s="97"/>
-      <c r="T3" s="97"/>
-      <c r="U3" s="97"/>
-      <c r="V3" s="97"/>
-      <c r="W3" s="97"/>
-      <c r="X3" s="98"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="79"/>
+      <c r="U3" s="79"/>
+      <c r="V3" s="79"/>
+      <c r="W3" s="79"/>
+      <c r="X3" s="80"/>
       <c r="Y3" s="11" t="s">
         <v>7</v>
       </c>
       <c r="Z3" s="13"/>
-      <c r="AA3" s="84"/>
-      <c r="AB3" s="85"/>
-      <c r="AC3" s="85"/>
-      <c r="AD3" s="85"/>
-      <c r="AE3" s="86"/>
-      <c r="AF3" s="87"/>
-      <c r="AG3" s="88"/>
-      <c r="AH3" s="88"/>
-      <c r="AI3" s="89"/>
-    </row>
-    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA3" s="66"/>
+      <c r="AB3" s="67"/>
+      <c r="AC3" s="67"/>
+      <c r="AD3" s="67"/>
+      <c r="AE3" s="68"/>
+      <c r="AF3" s="69"/>
+      <c r="AG3" s="70"/>
+      <c r="AH3" s="70"/>
+      <c r="AI3" s="71"/>
+    </row>
+    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="14" t="s">
         <v>13</v>
       </c>
@@ -1553,8 +1580,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C7" s="14" t="str">
         <f>$B$5&amp;"10."</f>
         <v>7.10.</v>
@@ -1563,7 +1590,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D8" s="20"/>
       <c r="E8" s="20"/>
       <c r="F8" s="20"/>
@@ -1596,7 +1623,7 @@
       <c r="AG8" s="20"/>
       <c r="AH8" s="20"/>
     </row>
-    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="21"/>
       <c r="B9" s="21"/>
       <c r="C9" s="21"/>
@@ -1638,7 +1665,7 @@
       <c r="AH9" s="21"/>
       <c r="AI9" s="21"/>
     </row>
-    <row r="10" spans="1:35" ht="11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
       <c r="A10" s="21"/>
       <c r="B10" s="21"/>
       <c r="C10" s="21"/>
@@ -1677,7 +1704,7 @@
       <c r="AH10" s="21"/>
       <c r="AI10" s="21"/>
     </row>
-    <row r="11" spans="1:35" ht="11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
       <c r="A11" s="21"/>
       <c r="B11" s="21"/>
       <c r="C11" s="21"/>
@@ -1714,7 +1741,7 @@
       <c r="AH11" s="21"/>
       <c r="AI11" s="21"/>
     </row>
-    <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="21"/>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
@@ -1753,7 +1780,7 @@
       <c r="AH12" s="21"/>
       <c r="AI12" s="21"/>
     </row>
-    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="21"/>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
@@ -1796,20 +1823,20 @@
       <c r="AH13" s="25"/>
       <c r="AI13" s="21"/>
     </row>
-    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="21"/>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
       <c r="D14" s="22"/>
-      <c r="E14" s="63" t="s">
+      <c r="E14" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="64"/>
-      <c r="K14" s="65"/>
+      <c r="F14" s="83"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="83"/>
+      <c r="I14" s="83"/>
+      <c r="J14" s="83"/>
+      <c r="K14" s="84"/>
       <c r="L14" s="41" t="s">
         <v>24</v>
       </c>
@@ -1839,18 +1866,18 @@
       <c r="AH14" s="43"/>
       <c r="AI14" s="21"/>
     </row>
-    <row r="15" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="21"/>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
       <c r="D15" s="22"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="67"/>
-      <c r="J15" s="67"/>
-      <c r="K15" s="68"/>
+      <c r="E15" s="85"/>
+      <c r="F15" s="86"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="86"/>
+      <c r="I15" s="86"/>
+      <c r="J15" s="86"/>
+      <c r="K15" s="87"/>
       <c r="L15" s="44"/>
       <c r="M15" s="45"/>
       <c r="N15" s="45"/>
@@ -1876,20 +1903,20 @@
       <c r="AH15" s="46"/>
       <c r="AI15" s="21"/>
     </row>
-    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="21"/>
       <c r="B16" s="21"/>
       <c r="C16" s="21"/>
       <c r="D16" s="22"/>
-      <c r="E16" s="63" t="s">
+      <c r="E16" s="82" t="s">
         <v>57</v>
       </c>
-      <c r="F16" s="64"/>
-      <c r="G16" s="64"/>
-      <c r="H16" s="64"/>
-      <c r="I16" s="64"/>
-      <c r="J16" s="64"/>
-      <c r="K16" s="65"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="83"/>
+      <c r="I16" s="83"/>
+      <c r="J16" s="83"/>
+      <c r="K16" s="84"/>
       <c r="L16" s="41" t="s">
         <v>59</v>
       </c>
@@ -1919,18 +1946,18 @@
       <c r="AH16" s="48"/>
       <c r="AI16" s="21"/>
     </row>
-    <row r="17" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="21"/>
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
       <c r="D17" s="22"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="67"/>
-      <c r="H17" s="67"/>
-      <c r="I17" s="67"/>
-      <c r="J17" s="67"/>
-      <c r="K17" s="68"/>
+      <c r="E17" s="85"/>
+      <c r="F17" s="86"/>
+      <c r="G17" s="86"/>
+      <c r="H17" s="86"/>
+      <c r="I17" s="86"/>
+      <c r="J17" s="86"/>
+      <c r="K17" s="87"/>
       <c r="L17" s="61" t="s">
         <v>60</v>
       </c>
@@ -1958,18 +1985,18 @@
       <c r="AH17" s="50"/>
       <c r="AI17" s="21"/>
     </row>
-    <row r="18" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="21"/>
       <c r="B18" s="21"/>
       <c r="C18" s="21"/>
       <c r="D18" s="22"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="70"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="70"/>
-      <c r="J18" s="70"/>
-      <c r="K18" s="71"/>
+      <c r="E18" s="88"/>
+      <c r="F18" s="89"/>
+      <c r="G18" s="89"/>
+      <c r="H18" s="89"/>
+      <c r="I18" s="89"/>
+      <c r="J18" s="89"/>
+      <c r="K18" s="90"/>
       <c r="L18" s="55"/>
       <c r="M18" s="56"/>
       <c r="N18" s="56"/>
@@ -1995,20 +2022,20 @@
       <c r="AH18" s="50"/>
       <c r="AI18" s="21"/>
     </row>
-    <row r="19" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="21"/>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
       <c r="D19" s="22"/>
-      <c r="E19" s="63" t="s">
+      <c r="E19" s="82" t="s">
         <v>56</v>
       </c>
-      <c r="F19" s="64"/>
-      <c r="G19" s="64"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="64"/>
-      <c r="K19" s="65"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="83"/>
+      <c r="I19" s="83"/>
+      <c r="J19" s="83"/>
+      <c r="K19" s="84"/>
       <c r="L19" s="55"/>
       <c r="M19" s="56"/>
       <c r="N19" s="56"/>
@@ -2034,18 +2061,18 @@
       <c r="AH19" s="50"/>
       <c r="AI19" s="21"/>
     </row>
-    <row r="20" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="21"/>
       <c r="B20" s="21"/>
       <c r="C20" s="21"/>
       <c r="D20" s="22"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="67"/>
-      <c r="G20" s="67"/>
-      <c r="H20" s="67"/>
-      <c r="I20" s="67"/>
-      <c r="J20" s="67"/>
-      <c r="K20" s="68"/>
+      <c r="E20" s="85"/>
+      <c r="F20" s="86"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="86"/>
+      <c r="I20" s="86"/>
+      <c r="J20" s="86"/>
+      <c r="K20" s="87"/>
       <c r="L20" s="55"/>
       <c r="M20" s="56"/>
       <c r="N20" s="56"/>
@@ -2071,18 +2098,18 @@
       <c r="AH20" s="50"/>
       <c r="AI20" s="21"/>
     </row>
-    <row r="21" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="21"/>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
       <c r="D21" s="22"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="70"/>
-      <c r="G21" s="70"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="70"/>
-      <c r="J21" s="70"/>
-      <c r="K21" s="71"/>
+      <c r="E21" s="88"/>
+      <c r="F21" s="89"/>
+      <c r="G21" s="89"/>
+      <c r="H21" s="89"/>
+      <c r="I21" s="89"/>
+      <c r="J21" s="89"/>
+      <c r="K21" s="90"/>
       <c r="L21" s="55"/>
       <c r="M21" s="56"/>
       <c r="N21" s="56"/>
@@ -2108,20 +2135,20 @@
       <c r="AH21" s="50"/>
       <c r="AI21" s="21"/>
     </row>
-    <row r="22" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="21"/>
       <c r="B22" s="21"/>
       <c r="C22" s="21"/>
       <c r="D22" s="22"/>
-      <c r="E22" s="72" t="s">
+      <c r="E22" s="91" t="s">
         <v>55</v>
       </c>
-      <c r="F22" s="73"/>
-      <c r="G22" s="73"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="73"/>
-      <c r="J22" s="73"/>
-      <c r="K22" s="74"/>
+      <c r="F22" s="92"/>
+      <c r="G22" s="92"/>
+      <c r="H22" s="92"/>
+      <c r="I22" s="92"/>
+      <c r="J22" s="92"/>
+      <c r="K22" s="93"/>
       <c r="L22" s="55"/>
       <c r="M22" s="56"/>
       <c r="N22" s="56"/>
@@ -2147,18 +2174,18 @@
       <c r="AH22" s="50"/>
       <c r="AI22" s="21"/>
     </row>
-    <row r="23" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="21"/>
       <c r="B23" s="21"/>
       <c r="C23" s="21"/>
       <c r="D23" s="22"/>
-      <c r="E23" s="75"/>
-      <c r="F23" s="76"/>
-      <c r="G23" s="76"/>
-      <c r="H23" s="76"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="76"/>
-      <c r="K23" s="77"/>
+      <c r="E23" s="94"/>
+      <c r="F23" s="95"/>
+      <c r="G23" s="95"/>
+      <c r="H23" s="95"/>
+      <c r="I23" s="95"/>
+      <c r="J23" s="95"/>
+      <c r="K23" s="96"/>
       <c r="L23" s="58"/>
       <c r="M23" s="59"/>
       <c r="N23" s="59"/>
@@ -2184,7 +2211,7 @@
       <c r="AH23" s="52"/>
       <c r="AI23" s="21"/>
     </row>
-    <row r="24" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="21"/>
       <c r="B24" s="21"/>
       <c r="C24" s="21"/>
@@ -2221,7 +2248,7 @@
       <c r="AH24" s="21"/>
       <c r="AI24" s="21"/>
     </row>
-    <row r="25" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="21"/>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
@@ -2258,7 +2285,7 @@
       <c r="AH25" s="21"/>
       <c r="AI25" s="21"/>
     </row>
-    <row r="26" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="21"/>
       <c r="B26" s="21"/>
       <c r="C26" s="21"/>
@@ -2300,7 +2327,7 @@
       <c r="AH26" s="21"/>
       <c r="AI26" s="21"/>
     </row>
-    <row r="27" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="21"/>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
@@ -2342,7 +2369,7 @@
       <c r="AH27" s="21"/>
       <c r="AI27" s="21"/>
     </row>
-    <row r="28" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="21"/>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
@@ -2383,7 +2410,7 @@
       <c r="AH28" s="21"/>
       <c r="AI28" s="21"/>
     </row>
-    <row r="29" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="21"/>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -2422,7 +2449,7 @@
       <c r="AH29" s="21"/>
       <c r="AI29" s="21"/>
     </row>
-    <row r="30" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="21"/>
       <c r="B30" s="21"/>
       <c r="C30" s="21"/>
@@ -2461,7 +2488,7 @@
       <c r="AH30" s="21"/>
       <c r="AI30" s="21"/>
     </row>
-    <row r="31" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="21"/>
       <c r="B31" s="21"/>
       <c r="C31" s="21"/>
@@ -2500,7 +2527,7 @@
       <c r="AH31" s="21"/>
       <c r="AI31" s="21"/>
     </row>
-    <row r="32" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="21"/>
       <c r="B32" s="21"/>
       <c r="C32" s="21"/>
@@ -2539,7 +2566,7 @@
       <c r="AH32" s="21"/>
       <c r="AI32" s="21"/>
     </row>
-    <row r="33" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="21"/>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -2576,7 +2603,7 @@
       <c r="AH33" s="21"/>
       <c r="AI33" s="21"/>
     </row>
-    <row r="34" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="21"/>
       <c r="B34" s="21"/>
       <c r="C34" s="21"/>
@@ -2615,7 +2642,7 @@
       <c r="AH34" s="17"/>
       <c r="AI34" s="21"/>
     </row>
-    <row r="35" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="21"/>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
@@ -2654,7 +2681,7 @@
       <c r="AH35" s="17"/>
       <c r="AI35" s="21"/>
     </row>
-    <row r="36" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="21"/>
       <c r="B36" s="21"/>
       <c r="C36" s="21"/>
@@ -2699,7 +2726,7 @@
       <c r="AH36" s="32"/>
       <c r="AI36" s="21"/>
     </row>
-    <row r="37" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="21"/>
       <c r="B37" s="21"/>
       <c r="C37" s="21"/>
@@ -2744,7 +2771,7 @@
       <c r="AH37" s="35"/>
       <c r="AI37" s="21"/>
     </row>
-    <row r="38" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="21"/>
       <c r="B38" s="21"/>
       <c r="C38" s="21"/>
@@ -2781,7 +2808,7 @@
       <c r="AH38" s="38"/>
       <c r="AI38" s="21"/>
     </row>
-    <row r="39" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="21"/>
       <c r="B39" s="21"/>
       <c r="C39" s="21"/>
@@ -2826,7 +2853,7 @@
       <c r="AH39" s="35"/>
       <c r="AI39" s="21"/>
     </row>
-    <row r="40" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="21"/>
       <c r="B40" s="21"/>
       <c r="C40" s="21"/>
@@ -2863,7 +2890,7 @@
       <c r="AH40" s="38"/>
       <c r="AI40" s="21"/>
     </row>
-    <row r="41" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="21"/>
       <c r="B41" s="21"/>
       <c r="C41" s="21"/>
@@ -2908,7 +2935,7 @@
       <c r="AH41" s="35"/>
       <c r="AI41" s="21"/>
     </row>
-    <row r="42" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="21"/>
       <c r="B42" s="21"/>
       <c r="C42" s="21"/>
@@ -2947,7 +2974,7 @@
       <c r="AH42" s="35"/>
       <c r="AI42" s="21"/>
     </row>
-    <row r="43" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="21"/>
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
@@ -2986,7 +3013,7 @@
       <c r="AH43" s="35"/>
       <c r="AI43" s="21"/>
     </row>
-    <row r="44" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="21"/>
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
@@ -3023,7 +3050,7 @@
       <c r="AH44" s="38"/>
       <c r="AI44" s="21"/>
     </row>
-    <row r="45" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="21"/>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
@@ -3062,7 +3089,7 @@
       <c r="AH45" s="17"/>
       <c r="AI45" s="21"/>
     </row>
-    <row r="46" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="21"/>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
@@ -3099,7 +3126,7 @@
       <c r="AH46" s="17"/>
       <c r="AI46" s="21"/>
     </row>
-    <row r="47" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="21"/>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
@@ -3140,7 +3167,7 @@
       <c r="AH47" s="21"/>
       <c r="AI47" s="21"/>
     </row>
-    <row r="48" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="21"/>
       <c r="B48" s="21"/>
       <c r="C48" s="21"/>
@@ -3179,7 +3206,7 @@
       <c r="AH48" s="21"/>
       <c r="AI48" s="21"/>
     </row>
-    <row r="49" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="21"/>
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
@@ -3218,7 +3245,7 @@
       <c r="AH49" s="21"/>
       <c r="AI49" s="21"/>
     </row>
-    <row r="50" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="21"/>
       <c r="B50" s="21"/>
       <c r="C50" s="21"/>
@@ -3257,7 +3284,7 @@
       <c r="AH50" s="21"/>
       <c r="AI50" s="21"/>
     </row>
-    <row r="51" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="21"/>
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
@@ -3294,7 +3321,7 @@
       <c r="AH51" s="21"/>
       <c r="AI51" s="21"/>
     </row>
-    <row r="52" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="21"/>
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
@@ -3336,7 +3363,7 @@
       <c r="AH52" s="21"/>
       <c r="AI52" s="21"/>
     </row>
-    <row r="53" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="21"/>
       <c r="B53" s="21"/>
       <c r="C53" s="21"/>
@@ -3377,7 +3404,7 @@
       <c r="AH53" s="17"/>
       <c r="AI53" s="21"/>
     </row>
-    <row r="54" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="21"/>
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
@@ -3416,7 +3443,7 @@
       <c r="AH54" s="17"/>
       <c r="AI54" s="21"/>
     </row>
-    <row r="55" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="21"/>
       <c r="B55" s="21"/>
       <c r="C55" s="21"/>
@@ -3455,7 +3482,7 @@
       <c r="AH55" s="17"/>
       <c r="AI55" s="21"/>
     </row>
-    <row r="56" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="21"/>
       <c r="B56" s="21"/>
       <c r="C56" s="21"/>
@@ -3494,7 +3521,7 @@
       <c r="AH56" s="17"/>
       <c r="AI56" s="21"/>
     </row>
-    <row r="57" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="21"/>
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
@@ -3531,7 +3558,7 @@
       <c r="AH57" s="17"/>
       <c r="AI57" s="21"/>
     </row>
-    <row r="58" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="21"/>
       <c r="B58" s="21"/>
       <c r="C58" s="21"/>
@@ -3570,7 +3597,7 @@
       <c r="AH58" s="17"/>
       <c r="AI58" s="21"/>
     </row>
-    <row r="59" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:35" s="20" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="21"/>
       <c r="B59" s="21"/>
       <c r="C59" s="21"/>
@@ -3609,7 +3636,7 @@
       <c r="AH59" s="17"/>
       <c r="AI59" s="21"/>
     </row>
-    <row r="60" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="21"/>
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
@@ -3646,7 +3673,7 @@
       <c r="AH60" s="17"/>
       <c r="AI60" s="21"/>
     </row>
-    <row r="61" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="21"/>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
@@ -3687,7 +3714,7 @@
       <c r="AH61" s="17"/>
       <c r="AI61" s="21"/>
     </row>
-    <row r="62" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="21"/>
       <c r="B62" s="21"/>
       <c r="C62" s="21"/>
@@ -3726,7 +3753,7 @@
       <c r="AH62" s="17"/>
       <c r="AI62" s="21"/>
     </row>
-    <row r="63" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D63" s="14"/>
       <c r="E63" s="14"/>
       <c r="F63" s="19"/>
@@ -3741,7 +3768,7 @@
       <c r="AG63" s="16"/>
       <c r="AH63" s="16"/>
     </row>
-    <row r="64" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E64" s="16"/>
       <c r="F64" s="18"/>
       <c r="T64" s="16"/>
@@ -3760,7 +3787,7 @@
       <c r="AG64" s="16"/>
       <c r="AH64" s="16"/>
     </row>
-    <row r="65" spans="4:34" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="4:34" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E65" s="14"/>
       <c r="U65" s="16"/>
       <c r="V65" s="16"/>
@@ -3777,453 +3804,458 @@
       <c r="AG65" s="16"/>
       <c r="AH65" s="16"/>
     </row>
-    <row r="66" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D66" s="14"/>
     </row>
-    <row r="67" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="68" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="69" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="70" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="71" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="14"/>
     </row>
-    <row r="72" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="73" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="74" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F74" s="14"/>
     </row>
-    <row r="75" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="76" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="77" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="78" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="79" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="80" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="81" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="82" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="83" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="84" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="85" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="86" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="87" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="88" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="89" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="90" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="91" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="92" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="93" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="94" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="95" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="96" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="97" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="98" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="99" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="100" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="101" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="102" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="103" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="104" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="105" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="106" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="107" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="108" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="109" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="110" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="111" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="112" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="113" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="114" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="115" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="116" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="117" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="118" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="119" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="120" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="121" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="122" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="123" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="124" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="125" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="E19:K21"/>
+    <mergeCell ref="E16:K18"/>
+    <mergeCell ref="E22:K23"/>
+    <mergeCell ref="E1:O1"/>
+    <mergeCell ref="E14:K15"/>
     <mergeCell ref="R1:X1"/>
     <mergeCell ref="AA1:AE1"/>
     <mergeCell ref="AF1:AI1"/>
@@ -4234,11 +4266,6 @@
     <mergeCell ref="E3:O3"/>
     <mergeCell ref="AA3:AE3"/>
     <mergeCell ref="AF3:AI3"/>
-    <mergeCell ref="E19:K21"/>
-    <mergeCell ref="E16:K18"/>
-    <mergeCell ref="E22:K23"/>
-    <mergeCell ref="E1:O1"/>
-    <mergeCell ref="E14:K15"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations disablePrompts="1" count="1">
